--- a/template_file/StockOutExportTemplate.xlsx
+++ b/template_file/StockOutExportTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-andum\Toho-Project\cmwi\backend\template_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38623CF7-5A0E-4664-B93E-CA88CC87699C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CDE739-8E26-4BF9-AF48-35E3C52AF654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4905" windowWidth="29040" windowHeight="15990" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
   </bookViews>
@@ -714,10 +714,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>5</v>

--- a/template_file/StockOutExportTemplate.xlsx
+++ b/template_file/StockOutExportTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-andum\Toho-Project\cmwi\backend\template_file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-andum\cmwi\backend-cmw\template_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CDE739-8E26-4BF9-AF48-35E3C52AF654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1B372-CCB9-40C7-A4AA-E1A7C86F7DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4905" windowWidth="29040" windowHeight="15990" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>Code</t>
   </si>
   <si>
-    <t>Operator</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -61,6 +58,9 @@
   </si>
   <si>
     <t>Stock Out</t>
+  </si>
+  <si>
+    <t>Requester</t>
   </si>
 </sst>
 </file>
@@ -629,7 +629,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
@@ -666,7 +666,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -684,7 +684,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -711,19 +711,19 @@
         <v>3</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="H7" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" s="8"/>
     </row>

--- a/template_file/StockOutExportTemplate.xlsx
+++ b/template_file/StockOutExportTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project-andum\cmwi\backend-cmw\template_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1B372-CCB9-40C7-A4AA-E1A7C86F7DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D883E6-1FF4-437F-8431-CDB54567F36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68B70A97-9B1A-4050-BAC0-10AB1B61C359}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve"> Department : 75 - EQUIPMENT ASSURANCE</t>
   </si>
   <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Dept.</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
@@ -61,6 +55,15 @@
   </si>
   <si>
     <t>Requester</t>
+  </si>
+  <si>
+    <t>Rack</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Specification</t>
   </si>
 </sst>
 </file>
@@ -179,15 +182,6 @@
         <color theme="1"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="1"/>
       </top>
@@ -208,7 +202,22 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -216,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -230,20 +239,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -617,47 +629,49 @@
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
     <col min="3" max="3" width="29.85546875" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
     <col min="5" max="5" width="30.5703125" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
     <col min="7" max="7" width="25.42578125" customWidth="1"/>
-    <col min="8" max="8" width="27.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="3"/>
+      <c r="B1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="12"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="1"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -665,17 +679,17 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="1"/>
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -683,17 +697,17 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="2"/>
+      <c r="A5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -702,46 +716,47 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>2</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
